--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_aysen.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_aysen.xlsx
@@ -404,7 +404,7 @@
         <v>26.86372887773938</v>
       </c>
       <c r="D2">
-        <v>1.821685708126751</v>
+        <v>3.567544748395812</v>
       </c>
       <c r="E2">
         <v>18.0965331785054</v>
@@ -429,7 +429,7 @@
         <v>20.66420664206642</v>
       </c>
       <c r="D3">
-        <v>1.59882005899705</v>
+        <v>2.387665198237885</v>
       </c>
       <c r="E3">
         <v>25.76617480136209</v>
@@ -454,7 +454,7 @@
         <v>26.06684084476377</v>
       </c>
       <c r="D4">
-        <v>1.863474997464246</v>
+        <v>3.623668639053255</v>
       </c>
       <c r="E4">
         <v>17.95898126173356</v>
@@ -479,7 +479,7 @@
         <v>25.39024390243902</v>
       </c>
       <c r="D5">
-        <v>1.859410430839002</v>
+        <v>3.52233676975945</v>
       </c>
       <c r="E5">
         <v>18.46153846153846</v>
@@ -504,7 +504,7 @@
         <v>27.34530938123753</v>
       </c>
       <c r="D6">
-        <v>1.926923076923077</v>
+        <v>4.073170731707317</v>
       </c>
       <c r="E6">
         <v>16.16294349540079</v>
@@ -529,7 +529,7 @@
         <v>28.23141706334676</v>
       </c>
       <c r="D7">
-        <v>1.76421188630491</v>
+        <v>3.514800514800515</v>
       </c>
       <c r="E7">
         <v>18.15844823556906</v>
@@ -554,7 +554,7 @@
         <v>21.45015105740181</v>
       </c>
       <c r="D8">
-        <v>3.637362637362637</v>
+        <v>16.55</v>
       </c>
       <c r="E8">
         <v>4.739336492890995</v>
@@ -579,7 +579,7 @@
         <v>29.23497267759563</v>
       </c>
       <c r="D9">
-        <v>2.022099447513812</v>
+        <v>4.945945945945946</v>
       </c>
       <c r="E9">
         <v>13.52833638025594</v>
@@ -604,7 +604,7 @@
         <v>24.48865228355282</v>
       </c>
       <c r="D10">
-        <v>1.514855687606112</v>
+        <v>2.408232118758435</v>
       </c>
       <c r="E10">
         <v>25.0126582278481</v>
@@ -629,7 +629,7 @@
         <v>19.41021126760564</v>
       </c>
       <c r="D11">
-        <v>1.687964338781575</v>
+        <v>2.510497237569061</v>
       </c>
       <c r="E11">
         <v>25.01381978993919</v>

--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_aysen.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_aysen.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>26.86372887773938</v>
+      </c>
+      <c r="C2">
         <v>28.03048232120036</v>
-      </c>
-      <c r="C2">
-        <v>26.86372887773938</v>
       </c>
       <c r="D2">
         <v>3.567544748395812</v>
       </c>
       <c r="E2">
-        <v>18.0965331785054</v>
+        <v>17.34327491634707</v>
       </c>
       <c r="F2">
         <v>64.56019190514752</v>
       </c>
       <c r="G2">
-        <v>17.34327491634707</v>
+        <v>18.0965331785054</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>20.66420664206642</v>
+      </c>
+      <c r="C3">
         <v>41.88191881918819</v>
-      </c>
-      <c r="C3">
-        <v>20.66420664206642</v>
       </c>
       <c r="D3">
         <v>2.387665198237885</v>
       </c>
       <c r="E3">
+        <v>12.71282633371169</v>
+      </c>
+      <c r="F3">
+        <v>61.52099886492622</v>
+      </c>
+      <c r="G3">
         <v>25.76617480136209</v>
-      </c>
-      <c r="F3">
-        <v>61.52099886492621</v>
-      </c>
-      <c r="G3">
-        <v>12.71282633371169</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>26.06684084476377</v>
+      </c>
+      <c r="C4">
         <v>27.59634225996081</v>
-      </c>
-      <c r="C4">
-        <v>26.06684084476377</v>
       </c>
       <c r="D4">
         <v>3.623668639053255</v>
       </c>
       <c r="E4">
+        <v>16.96362155077751</v>
+      </c>
+      <c r="F4">
+        <v>65.07739718748893</v>
+      </c>
+      <c r="G4">
         <v>17.95898126173356</v>
-      </c>
-      <c r="F4">
-        <v>65.07739718748894</v>
-      </c>
-      <c r="G4">
-        <v>16.96362155077751</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>25.39024390243902</v>
+      </c>
+      <c r="C5">
         <v>28.39024390243902</v>
-      </c>
-      <c r="C5">
-        <v>25.39024390243902</v>
       </c>
       <c r="D5">
         <v>3.52233676975945</v>
       </c>
       <c r="E5">
+        <v>16.5107057890563</v>
+      </c>
+      <c r="F5">
+        <v>65.02775574940523</v>
+      </c>
+      <c r="G5">
         <v>18.46153846153846</v>
-      </c>
-      <c r="F5">
-        <v>65.02775574940524</v>
-      </c>
-      <c r="G5">
-        <v>16.51070578905631</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>27.34530938123753</v>
+      </c>
+      <c r="C6">
         <v>24.55089820359281</v>
-      </c>
-      <c r="C6">
-        <v>27.34530938123753</v>
       </c>
       <c r="D6">
         <v>4.073170731707317</v>
       </c>
       <c r="E6">
-        <v>16.16294349540079</v>
+        <v>18.00262812089356</v>
       </c>
       <c r="F6">
         <v>65.83442838370566</v>
       </c>
       <c r="G6">
-        <v>18.00262812089356</v>
+        <v>16.16294349540079</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>28.23141706334676</v>
+      </c>
+      <c r="C7">
         <v>28.45111680703039</v>
-      </c>
-      <c r="C7">
-        <v>28.23141706334676</v>
       </c>
       <c r="D7">
         <v>3.514800514800515</v>
       </c>
       <c r="E7">
-        <v>18.15844823556906</v>
+        <v>18.01822855807432</v>
       </c>
       <c r="F7">
         <v>63.82332320635663</v>
       </c>
       <c r="G7">
-        <v>18.01822855807432</v>
+        <v>18.15844823556906</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>21.45015105740181</v>
+      </c>
+      <c r="C8">
         <v>6.042296072507553</v>
-      </c>
-      <c r="C8">
-        <v>21.45015105740181</v>
       </c>
       <c r="D8">
         <v>16.55</v>
       </c>
       <c r="E8">
-        <v>4.739336492890995</v>
+        <v>16.82464454976303</v>
       </c>
       <c r="F8">
         <v>78.43601895734596</v>
       </c>
       <c r="G8">
-        <v>16.82464454976303</v>
+        <v>4.739336492890995</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>29.23497267759563</v>
+      </c>
+      <c r="C9">
         <v>20.21857923497268</v>
-      </c>
-      <c r="C9">
-        <v>29.23497267759563</v>
       </c>
       <c r="D9">
         <v>4.945945945945946</v>
       </c>
       <c r="E9">
-        <v>13.52833638025594</v>
+        <v>19.56124314442413</v>
       </c>
       <c r="F9">
         <v>66.91042047531992</v>
       </c>
       <c r="G9">
-        <v>19.56124314442413</v>
+        <v>13.52833638025594</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>24.48865228355282</v>
+      </c>
+      <c r="C10">
         <v>41.52423648080695</v>
-      </c>
-      <c r="C10">
-        <v>24.48865228355282</v>
       </c>
       <c r="D10">
         <v>2.408232118758435</v>
       </c>
       <c r="E10">
-        <v>25.0126582278481</v>
+        <v>14.75105485232067</v>
       </c>
       <c r="F10">
         <v>60.23628691983122</v>
       </c>
       <c r="G10">
-        <v>14.75105485232067</v>
+        <v>25.0126582278481</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>19.41021126760564</v>
+      </c>
+      <c r="C11">
         <v>39.83274647887324</v>
-      </c>
-      <c r="C11">
-        <v>19.41021126760564</v>
       </c>
       <c r="D11">
         <v>2.510497237569061</v>
       </c>
       <c r="E11">
-        <v>25.01381978993919</v>
+        <v>12.18905472636816</v>
       </c>
       <c r="F11">
         <v>62.79712548369265</v>
       </c>
       <c r="G11">
-        <v>12.18905472636816</v>
+        <v>25.01381978993919</v>
       </c>
     </row>
   </sheetData>
